--- a/Result/profitability/3032.xlsx
+++ b/Result/profitability/3032.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.11</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.71125</v>
+        <v>-0.66375</v>
       </c>
       <c r="N2" t="n">
-        <v>22.3525</v>
+        <v>22.5075</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.27</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.755</v>
+        <v>-0.7137500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>22.19625</v>
+        <v>22.46625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7937500000000001</v>
+        <v>-0.8462500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>22.7425</v>
+        <v>22.96</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,16 +1018,16 @@
         <v>0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9612499999999999</v>
+        <v>-0.29125</v>
       </c>
       <c r="N5" t="n">
-        <v>22.5325</v>
+        <v>23.10375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3850000000000001</v>
+        <v>-0.355</v>
       </c>
       <c r="N6" t="n">
-        <v>23.62625</v>
+        <v>23.50875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4737500000000001</v>
+        <v>0.37125</v>
       </c>
       <c r="N7" t="n">
-        <v>23.84625</v>
+        <v>24.3925</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2899999999999999</v>
+        <v>0.30875</v>
       </c>
       <c r="N8" t="n">
-        <v>24.8675</v>
+        <v>24.99125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.44</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2387499999999999</v>
+        <v>0.23875</v>
       </c>
       <c r="N9" t="n">
         <v>25.395</v>
@@ -1645,7 +1645,7 @@
         <v>0.19</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2487499999999999</v>
+        <v>0.24875</v>
       </c>
       <c r="N10" t="n">
         <v>25.685</v>
@@ -1772,7 +1772,7 @@
         <v>0.47</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2737499999999999</v>
+        <v>0.27375</v>
       </c>
       <c r="N11" t="n">
         <v>26.115</v>
@@ -1899,7 +1899,7 @@
         <v>0.36</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2737499999999999</v>
+        <v>0.27375</v>
       </c>
       <c r="N12" t="n">
         <v>25.8825</v>
@@ -2026,7 +2026,7 @@
         <v>0.15</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2824999999999999</v>
+        <v>0.2825</v>
       </c>
       <c r="N13" t="n">
         <v>26.22625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3032</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2833</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2149</v>
+      </c>
+      <c r="E75" t="n">
+        <v>684</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="G75" t="n">
+        <v>274</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.68%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-94</v>
+      </c>
+      <c r="J75" t="n">
+        <v>180</v>
+      </c>
+      <c r="K75" t="n">
+        <v>113</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.38375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1764705882352942</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.9899999999999984</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04274611398963724</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.229357798165138</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2334014300306435</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
